--- a/crisscross_kit/crisscross/dna_source_plates/cargo_plates/sw_src004_pulldownhandles.xlsx
+++ b/crisscross_kit/crisscross/dna_source_plates/cargo_plates/sw_src004_pulldownhandles.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10322"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stellawang/Documents/gitrepos/Crisscross-Design/crisscross_kit/crisscross/dna_source_plates/cargo_plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22F25B3D-2331-EF44-8D25-C05C89FA8B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DBB8DE-C673-4843-93BB-99472548AE1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5580" yWindow="-21840" windowWidth="38060" windowHeight="20020" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2840" yWindow="680" windowWidth="22180" windowHeight="16400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All Data" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="595">
   <si>
     <t>well</t>
   </si>
@@ -1194,9 +1194,6 @@
     <t>NON-SLAT OLIGO</t>
   </si>
   <si>
-    <t>CARGO-SSW041DoublePurification5primetoehold-h2-position_32</t>
-  </si>
-  <si>
     <t>CARGO-SSW042DoublePurification3primetoehold-h2-position_32</t>
   </si>
   <si>
@@ -1398,9 +1395,6 @@
     <t>c14n0.ext10.10bpTH.A25</t>
   </si>
   <si>
-    <t>Cargo Handle For Slat Position 32, Side h2, Cargo ID SSW041DoublePurification5primetoehold</t>
-  </si>
-  <si>
     <t>Cargo Handle For Slat Position 32, Side h2, Cargo ID SSW042DoublePurification3primetoehold</t>
   </si>
   <si>
@@ -1743,9 +1737,6 @@
     <t>Checkpoint handle 6 (originally secondary purification handle) at position 32 of h5 side</t>
   </si>
   <si>
-    <t>sw_src004_checkpointhandles</t>
-  </si>
-  <si>
     <t>CARGO-PureHandle1-h2-position_32</t>
   </si>
   <si>
@@ -1774,13 +1765,55 @@
   </si>
   <si>
     <t>Cargo Handle For Slat Position 32, Side h5, Cargo ID PureHandle1, originally from SSW096</t>
+  </si>
+  <si>
+    <t>sw_src004_pulldownhandles</t>
+  </si>
+  <si>
+    <t>Cargo Handle For Slat Position 32, Side h2, Cargo ID SSW041DoublePurification5primetoehold; was previously CARGO-SSW041DoublePurification5primetoehold-h2-position_32</t>
+  </si>
+  <si>
+    <t>CARGO-PolyAWithToehold-h2-position_1</t>
+  </si>
+  <si>
+    <t>CARGO-PolyAWithToehold-h2-position_32</t>
+  </si>
+  <si>
+    <t>CARGO-PolyAWithToehold-h5-position_1</t>
+  </si>
+  <si>
+    <t>CARGO-PolyAWithToehold-h5-position_32</t>
+  </si>
+  <si>
+    <t>GGGCGCCAGGGTGCTGGTTTGCCCCAGCAGGTTCCAGTTTGG tt CACAACTACC AAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>CTTGAAAACATAGATGATGAAACAAAACAAA tt CACAACTACC AAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>CCTGGCCCTCTCCAACGTCAAAGGGCGACTTGACGGGGAAAG tt CACAACTACC AAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>TCTGTAAATTAACAATTTCATTTTTTTAATGGAAACAAGTTACAAAATC tt CACAACTACC AAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>Cargo Handle for purification with polyA, Slat Position 1, Side h2, Cargo ID PolyAWithToehold, ordered as SSW105</t>
+  </si>
+  <si>
+    <t>Cargo Handle for purification with polyA, Slat Position 32, Side h2, Cargo ID PolyAWithToehold, ordered as SSW106</t>
+  </si>
+  <si>
+    <t>Cargo Handle for purification with polyA, Slat Position 1, Side h5, Cargo ID PolyAWithToehold, ordered as SSW107</t>
+  </si>
+  <si>
+    <t>Cargo Handle for purification with polyA, Slat Position 32, Side h5, Cargo ID PolyAWithToehold, ordered as SSW108</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1804,6 +1837,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1868,7 +1907,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1884,6 +1923,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2223,10 +2263,10 @@
         <v>389</v>
       </c>
       <c r="C2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D2" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E2">
         <v>200</v>
@@ -2240,10 +2280,10 @@
         <v>389</v>
       </c>
       <c r="C3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E3">
         <v>200</v>
@@ -2257,10 +2297,10 @@
         <v>389</v>
       </c>
       <c r="C4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E4">
         <v>200</v>
@@ -2274,10 +2314,10 @@
         <v>389</v>
       </c>
       <c r="C5" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E5">
         <v>200</v>
@@ -2291,10 +2331,10 @@
         <v>389</v>
       </c>
       <c r="C6" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E6">
         <v>200</v>
@@ -2308,10 +2348,10 @@
         <v>389</v>
       </c>
       <c r="C7" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E7">
         <v>200</v>
@@ -2325,10 +2365,10 @@
         <v>389</v>
       </c>
       <c r="C8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D8" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E8">
         <v>200</v>
@@ -2342,10 +2382,10 @@
         <v>389</v>
       </c>
       <c r="C9" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D9" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E9">
         <v>200</v>
@@ -2359,10 +2399,10 @@
         <v>389</v>
       </c>
       <c r="C10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D10" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E10">
         <v>200</v>
@@ -2376,10 +2416,10 @@
         <v>389</v>
       </c>
       <c r="C11" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D11" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E11">
         <v>200</v>
@@ -2393,10 +2433,10 @@
         <v>389</v>
       </c>
       <c r="C12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D12" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E12">
         <v>200</v>
@@ -2410,10 +2450,10 @@
         <v>389</v>
       </c>
       <c r="C13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D13" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E13">
         <v>200</v>
@@ -2427,10 +2467,10 @@
         <v>389</v>
       </c>
       <c r="C14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D14" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E14">
         <v>200</v>
@@ -2444,10 +2484,10 @@
         <v>389</v>
       </c>
       <c r="C15" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D15" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="E15">
         <v>200</v>
@@ -2461,10 +2501,10 @@
         <v>389</v>
       </c>
       <c r="C16" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D16" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E16">
         <v>200</v>
@@ -2478,10 +2518,10 @@
         <v>389</v>
       </c>
       <c r="C17" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D17" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="E17">
         <v>200</v>
@@ -2495,10 +2535,10 @@
         <v>389</v>
       </c>
       <c r="C18" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D18" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E18">
         <v>200</v>
@@ -2512,10 +2552,10 @@
         <v>389</v>
       </c>
       <c r="C19" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E19">
         <v>200</v>
@@ -2529,10 +2569,10 @@
         <v>389</v>
       </c>
       <c r="C20" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D20" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E20">
         <v>200</v>
@@ -2546,10 +2586,10 @@
         <v>389</v>
       </c>
       <c r="C21" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="D21" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="E21">
         <v>200</v>
@@ -2563,10 +2603,10 @@
         <v>389</v>
       </c>
       <c r="C22" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D22" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E22">
         <v>200</v>
@@ -2580,10 +2620,10 @@
         <v>389</v>
       </c>
       <c r="C23" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D23" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E23">
         <v>200</v>
@@ -2597,10 +2637,10 @@
         <v>389</v>
       </c>
       <c r="C24" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E24">
         <v>200</v>
@@ -2614,10 +2654,10 @@
         <v>389</v>
       </c>
       <c r="C25" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="D25" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="E25">
         <v>200</v>
@@ -2631,10 +2671,10 @@
         <v>389</v>
       </c>
       <c r="C26" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="D26" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E26">
         <v>200</v>
@@ -2658,10 +2698,10 @@
         <v>389</v>
       </c>
       <c r="C29" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D29" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E29">
         <v>200</v>
@@ -2685,10 +2725,10 @@
         <v>389</v>
       </c>
       <c r="C32" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D32" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="E32">
         <v>200</v>
@@ -2712,10 +2752,10 @@
         <v>389</v>
       </c>
       <c r="C35" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D35" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="E35">
         <v>200</v>
@@ -2739,10 +2779,10 @@
         <v>389</v>
       </c>
       <c r="C38" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D38" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E38">
         <v>200</v>
@@ -2766,10 +2806,10 @@
         <v>389</v>
       </c>
       <c r="C41" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="D41" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E41">
         <v>200</v>
@@ -2793,10 +2833,10 @@
         <v>389</v>
       </c>
       <c r="C44" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="D44" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E44">
         <v>200</v>
@@ -2820,10 +2860,10 @@
         <v>389</v>
       </c>
       <c r="C47" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D47" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E47">
         <v>200</v>
@@ -2844,13 +2884,13 @@
         <v>53</v>
       </c>
       <c r="B50" t="s">
-        <v>390</v>
+        <v>571</v>
       </c>
       <c r="C50" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D50" t="s">
-        <v>458</v>
+        <v>582</v>
       </c>
       <c r="E50">
         <v>200</v>
@@ -2861,13 +2901,13 @@
         <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C51" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D51" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E51">
         <v>200</v>
@@ -2878,13 +2918,13 @@
         <v>55</v>
       </c>
       <c r="B52" t="s">
+        <v>572</v>
+      </c>
+      <c r="C52" t="s">
+        <v>576</v>
+      </c>
+      <c r="D52" t="s">
         <v>575</v>
-      </c>
-      <c r="C52" t="s">
-        <v>579</v>
-      </c>
-      <c r="D52" t="s">
-        <v>578</v>
       </c>
       <c r="E52">
         <v>200</v>
@@ -2895,13 +2935,13 @@
         <v>56</v>
       </c>
       <c r="B53" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C53" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D53" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E53">
         <v>200</v>
@@ -2912,13 +2952,13 @@
         <v>57</v>
       </c>
       <c r="B54" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="C54" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D54" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E54">
         <v>200</v>
@@ -2974,82 +3014,130 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B74" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="D74" t="s">
+        <v>591</v>
+      </c>
+      <c r="E74">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B75" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="D75" t="s">
+        <v>592</v>
+      </c>
+      <c r="E75">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B76" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="D76" t="s">
+        <v>593</v>
+      </c>
+      <c r="E76">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B77" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>590</v>
+      </c>
+      <c r="D77" t="s">
+        <v>594</v>
+      </c>
+      <c r="E77">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -3144,13 +3232,13 @@
         <v>101</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D98" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E98">
         <v>200</v>
@@ -3161,13 +3249,13 @@
         <v>102</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D99" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E99">
         <v>200</v>
@@ -3178,13 +3266,13 @@
         <v>103</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D100" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E100">
         <v>200</v>
@@ -3195,13 +3283,13 @@
         <v>104</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D101" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E101">
         <v>200</v>
@@ -3212,13 +3300,13 @@
         <v>105</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D102" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E102">
         <v>200</v>
@@ -3229,13 +3317,13 @@
         <v>106</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D103" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E103">
         <v>200</v>
@@ -3246,13 +3334,13 @@
         <v>107</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D104" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E104">
         <v>200</v>
@@ -3263,13 +3351,13 @@
         <v>108</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D105" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E105">
         <v>200</v>
@@ -3280,13 +3368,13 @@
         <v>109</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D106" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E106">
         <v>200</v>
@@ -3297,13 +3385,13 @@
         <v>110</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="D107" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E107">
         <v>200</v>
@@ -3314,13 +3402,13 @@
         <v>111</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D108" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E108">
         <v>200</v>
@@ -3331,13 +3419,13 @@
         <v>112</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="D109" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E109">
         <v>200</v>
@@ -3408,13 +3496,13 @@
         <v>125</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="D122" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E122">
         <v>200</v>
@@ -3425,13 +3513,13 @@
         <v>126</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D123" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E123">
         <v>200</v>
@@ -3442,13 +3530,13 @@
         <v>127</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="D124" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E124">
         <v>200</v>
@@ -3459,13 +3547,13 @@
         <v>128</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D125" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E125">
         <v>200</v>
@@ -3476,13 +3564,13 @@
         <v>129</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D126" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E126">
         <v>200</v>
@@ -3493,13 +3581,13 @@
         <v>130</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D127" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E127">
         <v>200</v>
@@ -3510,13 +3598,13 @@
         <v>131</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D128" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E128">
         <v>200</v>
@@ -3527,13 +3615,13 @@
         <v>132</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D129" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E129">
         <v>200</v>
@@ -3544,13 +3632,13 @@
         <v>133</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D130" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E130">
         <v>200</v>
@@ -3561,13 +3649,13 @@
         <v>134</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D131" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E131">
         <v>200</v>
@@ -3578,13 +3666,13 @@
         <v>135</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D132" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E132">
         <v>200</v>
@@ -3595,13 +3683,13 @@
         <v>136</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D133" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E133">
         <v>200</v>
@@ -4883,84 +4971,84 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>389</v>
@@ -5037,7 +5125,7 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B3" t="s">
         <v>389</v>
@@ -5066,159 +5154,171 @@
     </row>
     <row r="4" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>574</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="6" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="E6" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="F6" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="G6" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="H6" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="I6" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="J6" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="K6" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="L6" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="M6" s="7" t="s">
         <v>522</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="M6" s="7" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B7" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>525</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="H7" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="J7" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="K7" s="8" t="s">
         <v>532</v>
       </c>
-      <c r="J7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>533</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="M7" s="8" t="s">
         <v>534</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="M7" s="8" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="1:25" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -5236,342 +5336,354 @@
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>460</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>462</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>477</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>481</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="T3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>487</v>
+        <v>485</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
